--- a/docs/LALKITAB_UPAY_CHAHIYE.xlsx
+++ b/docs/LALKITAB_UPAY_CHAHIYE.xlsx
@@ -10,7 +10,8 @@
     <sheet name="START" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHAHIYE" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SAB_STHITI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MERE_FAISLE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SCOPE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MERE_FAISLE" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,16 +77,16 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001D4ED8"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001D4ED8"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +130,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F1F1F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2A8"/>
       </patternFill>
     </fill>
@@ -159,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -191,31 +197,43 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -583,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -704,12 +722,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>✅ उपाय पहले से है</t>
+          <t>✅ उपाय पूरा है (आपका दिया या बैंक में)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -732,105 +750,139 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>🔴 आपसे चाहिए — केवल इतने</t>
+          <t>🔵 अंतरिम उपाय लगा है — आप बाद में असली देंगे</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>📌 सबसे ज़रूरी बात — आपको केवल 6 स्थितियों के उत्तर देने हैं। बाकी सब या तो पहले से मौजूद है, या मैंने आपके ही दिए नियमों से निकाल लिया है। जो 🔴 लाल हैं वे 'CHAHIYE' शीट में अलग रखे हैं — वहीं भर दीजिए।</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>⬛ हट रहा है (लाल किताब का नियम नहीं)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>📌 अब कोई भी स्थिति उपाय के बिना नहीं है। जो 3 आप बाद में देंगे, उन पर अभी मेरा अंतरिम उपाय लगा है — असली आने पर वह अपने-आप बदल जाएगा, कोड बदले बिना। कैसे — यह 'SCOPE' शीट में है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>शीट-सूची</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>शीट</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>क्या है</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>स्थिति</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>CHAHIYE</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>केवल वे स्थितियाँ जिनका उत्तर आपसे चाहिए — यहीं भरें</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>🔴 भरें</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>SAB_STHITI</t>
+        <v>1</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>CHAHIYE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>सारी स्थितियाँ, विस्तार से — कब बनती हैं व उपाय कहाँ से आएगा</t>
+          <t>जो अब भी बाकी है — आप बाद में भरेंगे, अभी अंतरिम उपाय चल रहा है</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>📖 पढ़ें</t>
+          <t>🔵 बाद में</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>SAB_STHITI</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>सारी स्थितियाँ, विस्तार से — कब बनती हैं व उपाय कहाँ से आएगा</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>📖 पढ़ें</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>बाद में उपाय जोड़ने का ढाँचा — कोड बदले बिना कैसे अपडेट होगा</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>🔧 ढाँचा</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>MERE_FAISLE</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>जो फ़ैसले मैंने ख़ुद लिए (आपके कहे अनुसार) — बदलना हो तो बता दें</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>🔵 सूचना</t>
         </is>
@@ -839,11 +891,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -855,28 +907,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🔴 केवल ये 6 उत्तर चाहिए</t>
+          <t>🔵 ये 3 बाकी हैं — आप बाद में देंगे</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>इनके बिना उपाय अधूरा रहेगा। बाकी सब मैंने संभाल लिया है। जितना बता सकें उतना काफ़ी — 'पता नहीं' भी एक जवाब है।</t>
+          <t>अभी इन पर मेरा अंतरिम उपाय चल रहा है, इसलिए कोई स्थिति खाली नहीं है। जब असली उपाय दें, वे अपने-आप इनकी जगह ले लेंगे।</t>
         </is>
       </c>
     </row>
@@ -898,21 +950,21 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>यह कब बनती है</t>
+          <t>क्या बाकी है</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>मुझे क्या चाहिए</t>
+          <t>अभी क्या लगा है (अंतरिम)</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>✏️ आपका उत्तर</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
+          <t>✏️ असली उपाय / नियम</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -921,165 +973,95 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>ग्रह अस्त (combust)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ग्रह सूर्य के बहुत निकट — बल क्षीण। अभी केवल दिखता है, उपाय नहीं जुड़ता</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>लाल किताब में अस्त ग्रह का उपाय क्या है? क्या यह लाल किताब का नियम है भी, या केवल वैदिक का?</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr"/>
-    </row>
-    <row r="6" ht="64" customHeight="1">
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>गूंगा · बहरा · लंगड़ा · अंधा · मृत ग्रह</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>पाँचों की पक्की परिभाषा, और हर एक का अपना उपाय (या सबका एक ही?)</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>ग्रह की स्थापना-वस्तु + उसके कारक भाव की सेवा; और उस भाव की चाबी वाले ग्रह को सक्रिय करना (जिससे संपर्क दोबारा जुड़े)। 'मृत' में तीनों एक साथ ⇒ सबसे ऊपर प्राथमिकता</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ग्रह</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>रतौंध कुंडली (ratandh)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>विशेष स्थिति — अभी केवल हाँ/नहीं दिखता है</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>रतौंध की परिभाषा व उपाय दोनों चाहिए</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr"/>
-    </row>
-    <row r="7" ht="64" customHeight="1">
+          <t>भाव</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>बुनियाद (जड़) बिगड़ना</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>बुनियाद के पक्के जोड़ों की पूरी सूची — आपके संदेश में "पक्के जोड़े केवल ये हैं:" के बाद वाक्य कट गया था</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>✅ दिशा तय: उपाय **हमेशा जड़ वाले भाव के ग्रह का** — शाखा वाले ग्रह को बिल्कुल न छेड़ें। ✅ त्रिकोण नियम नहीं लगेगा — केवल पक्के जोड़े, हार्डकोडेड। ⚠️ पर **जोड़ों की सूची संदेश में नहीं आई** ("पक्के जोड़े केवल ये हैं:" के बाद वाक्य कट गया)। अभी मेरे पास केवल दो हैं: 9→5 और 2→8। पूरी सूची चाहिए</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ग्रह</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>गूंगा · बहरा · लंगड़ा · अंधा · मृत ग्रह</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>आपके नियम-दस्तावेज़ में नाम से हैं; परिभाषाएँ मैंने अनुमान से भरी हैं (MASTER.xlsx → MERE_NIYAM)</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>पहले परिभाषा तय हो, फिर उपाय। पाँचों के लिए अलग-अलग उपाय चाहिए या एक ही?</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr"/>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>भाव</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>बुनियाद (जड़) बिगड़ना</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>9वें (जड़) में पापी/नीच ग्रह ⇒ 5वें के उच्च ग्रह का फल भी ख़राब। दूसरा जोड़ा: 2रा ⇒ 8वाँ</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>जड़ ठीक करने का उपाय क्या है — जड़ वाले भाव के ग्रह का, या शाखा वाले भाव के ग्रह का? और क्या त्रिकोण नियम (हर भाव की जड़ = 5वाँ व 9वाँ) लगाऊँ या केवल आपके दिए दो जोड़े?</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr"/>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
           <t>समय</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>वर्षफल का वर्ष अशुभ निकले</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>वर्ष-कुंडली में ग्रह ऐसे भावों में चले जाएँ कि उस वर्ष का निष्कर्ष अशुभ बने</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>क्या वर्षफल के लिए अलग (वर्ष-भर चलने वाले) उपाय होते हैं, या वही ग्रह-वार उपाय ही चलेंगे? कोई वर्ष-विशेष उपाय-तालिका है?</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>अन्य</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>आयु-योग अशुभ निकले</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>जैसे 'सूर्य राहु के साथ ⇒ आयु 0'</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>आयु-योग अशुभ हो तो उपाय क्या? यह संवेदनशील विषय है — आप बताएँ कि स्क्रीन पर इसे दिखाना भी चाहिए या नहीं</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>💡 अगर किसी का उत्तर न हो — बस 'पता नहीं' लिख दें। मैं उस स्थिति पर उपाय के बजाय केवल चेतावनी दिखाऊँगा, और स्क्रीन पर लिख दूँगा कि इसका उपाय-पाठ उपलब्ध नहीं। गलत उपाय देने से बेहतर है कुछ न देना।</t>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>क्या वर्ष-भर चलने वाली अलग उपाय-तालिका है, या ग्रह-वार उपाय ही चलेंगे?</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>उस वर्ष-कुंडली में जो ग्रह अशुभ बैठे हैं, उन्हीं के ग्रह-वार उपाय — पर **जन्मदिन से शुरू करके पूरे वर्ष** चलाए जाएँ (एक बार का नहीं)। प्राथमिकता उस ग्रह की जो उस वर्ष सबसे अशुभ भाव में गया हो</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>💡 जब भी दें — सीधे इसी शीट में लिख दीजिए, या अलग संदेश में। मैं वही पाठ ज्यों-का-त्यों उपाय-बैंक में डाल दूँगा; कोड बदलने की ज़रूरत नहीं पड़ेगी (देखें SCOPE शीट)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>⛔ जो चीज़ हट रही है — ग्रह अस्त (combust)। आपने कहा "लाल किताब के नियम के अनुसार ग्रह अस्त नहीं होता", इसलिए वैदिक अंशों वाली वह पूरी गणना व दृश्य हटेगा। इसका कोई उपाय नहीं चाहिए।</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1157,7 +1139,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>ग्रह का निष्कर्ष अशुभ</t>
         </is>
@@ -1187,7 +1169,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>ग्रह नीच भाव में</t>
         </is>
@@ -1217,7 +1199,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>निष्कर्ष 'मध्यम' पर ग्रह पीड़ित है</t>
         </is>
@@ -1247,7 +1229,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>सोया / सुप्त ग्रह</t>
         </is>
@@ -1277,7 +1259,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>ग्रह कच्चे घर में</t>
         </is>
@@ -1307,7 +1289,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>अशुभ ग्रह अपने पक्के घर में</t>
         </is>
@@ -1337,7 +1319,7 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>ग्रह का 'अशुभ वर्ष' चल रहा हो</t>
         </is>
@@ -1367,24 +1349,24 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>ग्रह अस्त (combust)</t>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>❌ ग्रह अस्त (combust) — हट रहा है</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ग्रह सूर्य के बहुत निकट — बल क्षीण। अभी केवल दिखता है, उपाय नहीं जुड़ता</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+          <t>अभी कोड वैदिक अंशों से अस्त गिनता है (चन्द्र 12°, मंगल 17°, बुध 13°, गुरु 11°, शुक्र 9°, शनि 15°)</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>⬛ हट रहा है</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>⚠️ लाल किताब में अस्त ग्रह का उपाय क्या है? क्या यह लाल किताब का नियम है भी, या केवल वैदिक का?</t>
+          <t>आपका उत्तर: "लाल किताब के नियम के अनुसार ग्रह अस्त नहीं होता।" ⇒ यह पूरी गणना व दृश्य हटेगा। कोई उपाय नहीं चाहिए</t>
         </is>
       </c>
     </row>
@@ -1397,24 +1379,24 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>रतौंध कुंडली (ratandh)</t>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>रतौंध कुंडली — रात की अंधी किस्मत</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>विशेष स्थिति — अभी केवल हाँ/नहीं दिखता है</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+          <t>भाव 4 में सूर्य और साथ ही भाव 7 में शनि। (भाव 4 = चन्द्र का पक्का घर/रात; भाव 7 = शुक्र/सूर्यास्त। दिन का राजा रात में डूबा, और सूर्यास्त के बाद का समय शनि के कब्ज़े में) ⇒ सूर्यास्त के बाद 'किस्मत की आँखें' काम करना बंद कर देती हैं</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>✅ उपाय है</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>⚠️ रतौंध की परिभाषा व उपाय दोनों चाहिए</t>
+          <t>आपका दिया पूरा उपाय: (1) परहेज़ ही मुख्य उपाय — बड़े फ़ैसले, दस्तख़त, बड़ा लेन-देन व नया काम सूर्यास्त के बाद कभी नहीं; (2) सूर्य को बल — तांबे के बर्तन में गंगाजल/शुद्ध जल घर में रखें, रात को दूध से सख़्त परहेज़ (दिन में ठीक); (3) शनि का ज़हर — काली लकड़ी की बांसुरी में चीनी भरकर सुनसान जगह ज़मीन में दबाएँ, और रात को काले/गहरे नीले कपड़े न पहनें। ✅ पहचान कोड में पहले से सही बनी है — केवल यह उपाय-पाठ जुड़ना है</t>
         </is>
       </c>
     </row>
@@ -1427,24 +1409,24 @@
           <t>ग्रह</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>गूंगा · बहरा · लंगड़ा · अंधा · मृत ग्रह</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>आपके नियम-दस्तावेज़ में नाम से हैं; परिभाषाएँ मैंने अनुमान से भरी हैं (MASTER.xlsx → MERE_NIYAM)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+          <t>पाँच अलग स्थितियाँ — ग्रह का संपर्क कटा होना। परिभाषाएँ अभी मेरी अनुमानित हैं (MASTER.xlsx → MERE_NIYAM)</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>🔵 अंतरिम — आप बाद में देंगे</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ पहले परिभाषा तय हो, फिर उपाय। पाँचों के लिए अलग-अलग उपाय चाहिए या एक ही?</t>
+          <t>⏳ आप बाद में देंगे। तब तक मेरा अंतरिम उपाय: ग्रह की स्थापना-वस्तु + उसके कारक भाव की सेवा; और उस भाव की चाबी वाले ग्रह को सक्रिय करना (जिससे संपर्क दोबारा जुड़े)। 'मृत' में तीनों एक साथ ⇒ सबसे ऊपर प्राथमिकता</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1439,7 @@
           <t>टक्कर</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>टक्कर — ग्रह अपने से आठवें वाले को खराब करे</t>
         </is>
@@ -1487,7 +1469,7 @@
           <t>टक्कर</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>विश्वासघात (धोखे की टक्कर)</t>
         </is>
@@ -1517,7 +1499,7 @@
           <t>टक्कर</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>साझी चोट (साझी दीवार)</t>
         </is>
@@ -1547,7 +1529,7 @@
           <t>टक्कर</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>अचानक चोट (अंधी टक्कर)</t>
         </is>
@@ -1577,7 +1559,7 @@
           <t>टक्कर</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>उपाय से ही कोई नई चोट जाग जाए</t>
         </is>
@@ -1607,7 +1589,7 @@
           <t>भाव</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>सोया भाव</t>
         </is>
@@ -1637,24 +1619,24 @@
           <t>भाव</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>बुनियाद (जड़) बिगड़ना</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9वें (जड़) में पापी/नीच ग्रह ⇒ 5वें के उच्च ग्रह का फल भी ख़राब। दूसरा जोड़ा: 2रा ⇒ 8वाँ</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+          <t>जड़ वाले भाव में पापी/नीच ग्रह ⇒ शाखा वाले भाव के उच्च ग्रह का फल भी सड़ जाता है। (पेड़ की जड़ में ज़हर हो तो टहनी पर कितना भी पानी डालो, फल सड़ेगा ही)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>🟠 आधा तय — सूची बाकी</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>⚠️ जड़ ठीक करने का उपाय क्या है — जड़ वाले भाव के ग्रह का, या शाखा वाले भाव के ग्रह का? और क्या त्रिकोण नियम (हर भाव की जड़ = 5वाँ व 9वाँ) लगाऊँ या केवल आपके दिए दो जोड़े?</t>
+          <t>✅ दिशा तय: उपाय **हमेशा जड़ वाले भाव के ग्रह का** — शाखा वाले ग्रह को बिल्कुल न छेड़ें। ✅ त्रिकोण नियम नहीं लगेगा — केवल पक्के जोड़े, हार्डकोडेड। ⚠️ पर **जोड़ों की सूची संदेश में नहीं आई** ("पक्के जोड़े केवल ये हैं:" के बाद वाक्य कट गया)। अभी मेरे पास केवल दो हैं: 9→5 और 2→8। पूरी सूची चाहिए</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1649,7 @@
           <t>भाव</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>भाव पर पाप-दृष्टि</t>
         </is>
@@ -1697,7 +1679,7 @@
           <t>युति</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>विशेष युति / ग्रहण दोष (8 सूचीबद्ध)</t>
         </is>
@@ -1727,7 +1709,7 @@
           <t>युति</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>मसनूई (कृत्रिम) ग्रह अशुभ बने</t>
         </is>
@@ -1757,7 +1739,7 @@
           <t>युति</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>भाव 8 — सांझी गद्दी की पक्की दुश्मनी</t>
         </is>
@@ -1787,7 +1769,7 @@
           <t>युति</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>मुकाबले के ग्रह — कोई भी दो कट्टर शत्रु एक भाव में</t>
         </is>
@@ -1817,7 +1799,7 @@
           <t>ऋण</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>नौ पैतृक ऋण</t>
         </is>
@@ -1847,7 +1829,7 @@
           <t>शाप</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>पूर्व-जन्म शाप</t>
         </is>
@@ -1877,7 +1859,7 @@
           <t>दोष</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>मांगलिक</t>
         </is>
@@ -1907,7 +1889,7 @@
           <t>दोष</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>साढ़े साती / ढैय्या</t>
         </is>
@@ -1937,7 +1919,7 @@
           <t>समय</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>वर्षफल का वर्ष अशुभ निकले</t>
         </is>
@@ -1947,14 +1929,14 @@
           <t>वर्ष-कुंडली में ग्रह ऐसे भावों में चले जाएँ कि उस वर्ष का निष्कर्ष अशुभ बने</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>🔵 अंतरिम — आप बाद में देंगे</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>⚠️ क्या वर्षफल के लिए अलग (वर्ष-भर चलने वाले) उपाय होते हैं, या वही ग्रह-वार उपाय ही चलेंगे? कोई वर्ष-विशेष उपाय-तालिका है?</t>
+          <t>⏳ आप बाद में देंगे। तब तक मेरा अंतरिम उपाय: उस वर्ष-कुंडली में जो ग्रह अशुभ बैठे हैं, उन्हीं के ग्रह-वार उपाय — पर **जन्मदिन से शुरू करके पूरे वर्ष** चलाए जाएँ (एक बार का नहीं)। प्राथमिकता उस ग्रह की जो उस वर्ष सबसे अशुभ भाव में गया हो</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1949,7 @@
           <t>समय</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>35-साला चक्र में अशुभ ग्रह का खंड चल रहा हो</t>
         </is>
@@ -1997,7 +1979,7 @@
           <t>अन्य</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>वर्जित कर्म (न करें)</t>
         </is>
@@ -2027,7 +2009,7 @@
           <t>अन्य</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>अशुभ लक्षण दिख रहे हों</t>
         </is>
@@ -2057,24 +2039,24 @@
           <t>अन्य</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>आयु-योग अशुभ निकले</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>जैसे 'सूर्य राहु के साथ ⇒ आयु 0'</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>🔴 आपसे चाहिए</t>
+          <t>जैसे 'सूर्य + राहु ⇒ आयु 0'। लाल किताब में सूर्य = प्राण और राहु = ज़हर/ग्रहण; दोनों साथ (विशेषकर भाव 1, 5 या 8 में) ⇒ पूर्ण सूर्य-ग्रहण ⇒ प्रतीकात्मक 'आयु 0'</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>✅ उपाय है</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>⚠️ आयु-योग अशुभ हो तो उपाय क्या? यह संवेदनशील विषय है — आप बताएँ कि स्क्रीन पर इसे दिखाना भी चाहिए या नहीं</t>
+          <t>आपका दिया नियम: स्क्रीन पर **'आयु 0', 'मृत्यु' या 'मृत्यु योग' कभी न छपे** — डराना उद्देश्य नहीं। इसकी जगह 5-स्तरीय वर्गीकरण: बालारिष्ट/अति-अल्प (0–12) · अल्प (12–32) · मध्यम (32–64) · दीर्घ (64–80) · पूर्ण (80–120)। 'आयु 0' वाला योग ⇒ वर्ग 1 'बालारिष्ट योग / प्राण-कष्ट की आशंका', लाल रंग में चेतावनी, और **साथ ही तुरंत उपाय** ताकि पढ़ने वाले को समाधान भी मिले</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2069,7 @@
           <t>अन्य</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>रोग / संतान सम्बन्धी</t>
         </is>
@@ -2118,6 +2100,641 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🔧 बाद में उपाय जोड़ने का ढाँचा</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>आपने कहा — बाकी उपाय बाद में देंगे, और अपडेट आसान रहे। इसके लिए यह ढाँचा बन रहा है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>मूल विचार — हर स्थिति का एक स्थायी कोड, और उपाय अलग फ़ाइल में</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>उपाय का पाठ कोड में कहीं नहीं लिखा जाएगा। हर स्थिति को एक स्थायी कोड मिलेगा (जैसे RATANDH, BUNIYAD, GUNGA_GRAH), और सारे उपाय एक अलग फ़ाइल में उसी कोड के नीचे रहेंगे। इसलिए नया उपाय जोड़ना = उस फ़ाइल में एक प्रविष्टि भरना। कोड को छूने की ज़रूरत कभी नहीं पड़ेगी — न प्रोग्रामर की, न दोबारा जाँच की।</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>खाना</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>क्या भरा जाएगा</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>उदाहरण (रतौंध)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>अभी की हालत</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>स्थिति का स्थायी कोड — कभी नहीं बदलेगा</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>RATANDH</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>मैं तय करूँगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>naam</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>स्क्रीन पर दिखने वाला नाम</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>रतौंध कुंडली — रात की अंधी किस्मत</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>तय</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>pehchan</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>कुंडली में यह कब बनती है (गणना की शर्त)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>भाव 4 में सूर्य और भाव 7 में शनि</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>✅ कोड में पहले से सही</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>phal</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>क्या फल होगा — सादी भाषा में</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>सूर्यास्त के बाद बुद्धि व भाग्य साथ नहीं देते; रात के फ़ैसले नुकसान देते हैं</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>आपका दिया</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>parhez</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>क्या न करें (सूची)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>सूर्यास्त के बाद बड़े फ़ैसले, दस्तख़त, बड़ा लेन-देन नहीं; रात को दूध नहीं; रात को काले/नीले कपड़े नहीं</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>आपका दिया</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>upay</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>क्या करें (सूची)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>तांबे के बर्तन में गंगाजल घर में रखें; काली बांसुरी में चीनी भरकर सुनसान जगह दबाएँ</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>आपका दिया</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>darja</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>यह पाठ पक्का है या अंतरिम</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>final / anumanit / lambit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>🏷️ 'दर्जा' खाना ही सबसे काम का है</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>दर्जा</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>मतलब</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>स्क्रीन पर</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>कब बदलेगा</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>आपका दिया पक्का उपाय</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>सामान्य रूप से दिखेगा</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>कभी नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>anumanit</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>मैंने आपके नियमों से निकाला</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>साथ में 'अनुमानित' का चिह्न</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>आप पक्का पाठ दें तब</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>अभी अंतरिम उपाय चल रहा है</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>'अंतरिम — पूरा उपाय आना बाकी' लिखा रहेगा</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>आप असली उपाय दें तब</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>✅ इसका फ़ायदा — जातक को कभी खाली स्क्रीन नहीं दिखेगी। जहाँ पक्का उपाय नहीं है वहाँ अंतरिम चलेगा, पर साफ़ लिखा रहेगा कि यह अंतरिम है। और जब आप असली पाठ दें, केवल एक प्रविष्टि बदलने से वह हर जगह अपने-आप लग जाएगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>📋 शुरुआती कोड-सूची (जो स्थितियाँ अभी लंबित हैं)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>कोड</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>स्थिति</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>अभी का दर्जा</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>किसका इंतज़ार</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>GUNGA_GRAH</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>गूंगा ग्रह</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>परिभाषा + उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>BEHRA_GRAH</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>बहरा ग्रह</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>परिभाषा + उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>LANGDA_GRAH</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>लंगड़ा ग्रह</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>परिभाषा + उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>ANDHA_GRAH</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>अंधा ग्रह</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>परिभाषा + उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>MRIT_GRAH</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>मृत ग्रह</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>परिभाषा + उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>BUNIYAD</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>बुनियाद (जड़) बिगड़ना</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>जोड़ों की पूरी सूची</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>VARSH_ASHUBH</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>वर्षफल का वर्ष अशुभ</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>lambit</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>वर्ष-भर की उपाय-विधि</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>RATANDH</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>रतौंध कुंडली</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>final ✅</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>— कुछ नहीं, पूरा मिल गया</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>AYU_YOG</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>आयु-योग (5 वर्ग)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>final ✅</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>— कुछ नहीं, पूरा मिल गया</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2178,12 +2795,12 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>बुध का पक्का घर — 6,7 या 7?</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>6, 7 (आपकी नई सूची)</t>
         </is>
@@ -2193,18 +2810,18 @@
           <t>आपका सबसे ताज़ा व स्पष्ट निर्देश यही था ('अपनी कोर डिक्शनरी को इस सटीक डेटा से रिप्लेस करें')। इससे भाव 6 के दो कारक बनते हैं (बुध + केतु) — पर वे शत्रु नहीं, इसलिए भाव 8 वाला युद्धक्षेत्र अकेला ही रहता है</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>केतु का भाव 3 — नीच है या नहीं?</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>हाँ — मुख्य नीच। केतु: मुख्य 3, 6 · गौण 8</t>
         </is>
@@ -2214,18 +2831,18 @@
           <t>'नीच = उच्च से सातवाँ' नियम नौ के नौ ग्रहों पर सही बैठता है और आपने उसे पुष्ट किया है। केतु उच्च 9, 12 ⇒ सातवाँ = 3, 6। आपकी सूची में 3 शायद लिखने से रह गया</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>राहु/केतु के गौण नीच का वज़न</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>मुख्य नीच = पूरा वज़न · गौण नीच = आधा</t>
         </is>
@@ -2235,18 +2852,18 @@
           <t>आपने ख़ुद 'मुख्यतः' लिखकर दो दर्जे बताए। राहु: मुख्य 9, 12 · गौण 8, 11। इससे पुरानी शीट की 'राहु नीच = 8, 9' वाली प्रविष्टि भी समझ आ जाती है — 9 मुख्य था, 8 गौण</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>मसनूई कमिट 0df42e2 — रखें या हटाएँ?</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>रखें</t>
         </is>
@@ -2256,18 +2873,18 @@
           <t>वह हिस्सा अलग-थलग है, आपके दोनों उदाहरणों पर हूबहू सही निकला, और 300 कुंडलियों पर जाँचा जा चुका है। उसमें पक्का-घर की जो दो गलत प्रविष्टियाँ गई हैं, वे सुधार #5 में अपने-आप ठीक हो जाएँगी</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>MERE_NIYAM के 12 नियम</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>मेरी परिभाषाएँ लागू; स्क्रीन पर 'अनुमानित' लिखा रहेगा</t>
         </is>
@@ -2277,18 +2894,18 @@
           <t>इनके बिना पाँच स्थितियाँ (गूंगा, बहरा, लंगड़ा, अंधा, मृत) चल ही नहीं सकतीं। 'अनुमानित' का चिह्न रहेगा, इसलिए कभी भी बदला जा सकता है</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SCOPE के 6 प्रस्तुति-निर्णय</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>मेरी सिफ़ारिशें लागू</t>
         </is>
@@ -2298,18 +2915,18 @@
           <t>ये ज्योतिष के नहीं, केवल दिखावट के फ़ैसले हैं — इनसे फलादेश नहीं बदलता</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr"/>
+      <c r="E10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>मंगल का 'विशेष' — 13/15 बनाम जागृति 28</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>शीट जैसी है वैसी ही रहने दूँ</t>
         </is>
@@ -2319,18 +2936,18 @@
           <t>मंगल अकेला ग्रह है जिसमें शुभ व अशुभ की दो अलग तिथियाँ दी हैं — यह जानबूझकर लगता है, गलती नहीं। बिना पक्के प्रमाण के इसे बदलना ठीक नहीं</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>वर्षफल तालिका की 30 टूटी पंक्तियाँ</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>छेड़ूँ नहीं; स्क्रीन पर उन आयु पर चिह्न लगेगा</t>
         </is>
@@ -2340,18 +2957,18 @@
           <t>बाकी ग्यारह भावों का चाल-नियम मुझे नहीं मिला, इसलिए सही पंक्ति क्या हो यह मैं नहीं बना सकता। अंदाज़े से भरने पर हर उस आयु का वर्षफल ग़लत निकलेगा — इससे बेहतर है सच बता देना</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>35-साला चक्र की सीमाएँ</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>पहले तय तालिका ही चलेगी (राहु 7–12 · केतु 13–15 · गुरु 16–21)</t>
         </is>
@@ -2361,18 +2978,18 @@
           <t>वह पूरे गणित के साथ दी गई थी (6+6+3+6+2+1+3+6+2 = 35)। बाद वाला ज़िक्र 'जैसे' कहकर उदाहरण के तौर पर था, इसलिए उसे रोज़मर्रा की भूल मानकर तय तालिका पर टिका हूँ</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>आयु-योग (जैसे 'सूर्य+राहु ⇒ आयु 0')</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>स्क्रीन पर आयु का अंक नहीं दिखाऊँगा</t>
         </is>
@@ -2382,10 +2999,10 @@
           <t>यह संवेदनशील है और डरा सकता है। इसकी जगह 'इस योग हेतु सावधानी व उपाय' लिखकर उपाय दूँगा। आप कहें तो पूरा दिखा दूँगा</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
+      <c r="E14" s="17" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>⏱️ अगर सब ठीक लगें तो कुछ लिखने की ज़रूरत नहीं — मैं इन्हीं पर चलूँगा। जो बदलना हो केवल उसी पंक्ति में लिख दें।</t>
         </is>

--- a/docs/LALKITAB_UPAY_CHAHIYE.xlsx
+++ b/docs/LALKITAB_UPAY_CHAHIYE.xlsx
@@ -12,6 +12,7 @@
     <sheet name="SAB_STHITI" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="SCOPE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MERE_FAISLE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SEEDHI" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2740,7 +2741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2991,18 +2992,123 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>स्क्रीन पर आयु का अंक नहीं दिखाऊँगा</t>
+          <t>5 वर्ग; अंक कभी नहीं दिखेगा</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>यह संवेदनशील है और डरा सकता है। इसकी जगह 'इस योग हेतु सावधानी व उपाय' लिखकर उपाय दूँगा। आप कहें तो पूरा दिखा दूँगा</t>
+          <t>आपने पुष्टि कर दी — बालारिष्ट (0–12) · अल्प (12–32) · मध्यम (32–64) · दीर्घ (64–80) · पूर्ण (80–120)। 'आयु 0' ⇒ वर्ग 1, लाल चेतावनी, और साथ ही तुरंत उपाय</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr"/>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>बुनियाद के जोड़े — पूरी सूची</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>केवल दो जोड़े: 9→5 और 2→8</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>आपने त्रिकोण लूप साफ़ मना कर दिया और कहा 'केवल पक्के जोड़े, हार्डकोडेड'। सूची कट गई थी, पर मैं बाकी जोड़े **गढ़ूँगा नहीं** — दो पक्के जोड़ों से चलाना, दस अनुमानित जोड़ों से बेहतर है। आप और दें तो एक प्रविष्टि जोड़ने भर की बात है</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>राहु भाव 6 / केतु भाव 12</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>उच्च तो हैं, पर 'उच्च पर अंतर्निहित भंग'</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>दोनों के भंग-नियम कहते हैं 'शुभ फल नहीं'। दोनों आईने जैसे हैं (राहु 6 ↔ केतु 12) ⇒ जानबूझकर है। फल: ग्रह वहाँ उच्च गिना जाएगा पर उच्च का लाभ नहीं मिलेगा — और यही स्क्रीन पर लिखा रहेगा</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>शुक्र का 'विशेष' (खाली था)</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>50वें दिन व 25वें वर्ष</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>शुक्र की जागृति आयु 25 है, और बुध (68/34) व शनि (72/36) में दिन = 2×वर्ष। इसी पैटर्न से 50</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>grah_chakra का 'क्रम' कॉलम</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>हटाएँ; उसकी जगह 35-साला दशा से पड़ोसी ग्रह</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>उस कॉलम का अपना नियम ही तय नहीं — 9 में से 6 पंक्तियाँ किसी क्रम से नहीं बनतीं, और राहु की पंक्ति में शीट ने ख़ुद '(?)' लिखा है</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>गूंगा · बहरा · लंगड़ा · अंधा · मृत</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>नई सुसंगत सीढ़ी बनाई (अलग शीट देखें)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>अब दृष्टि व सोया के नियम तय हो चुके हैं, इसलिए पाँचों को तीन गणना-योग्य संकेतों (बोल · सुनना · साथी) पर टिकाकर एक-दूसरे से न टकराने वाली सीढ़ी बना दी है</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>⏱️ अगर सब ठीक लगें तो कुछ लिखने की ज़रूरत नहीं — मैं इन्हीं पर चलूँगा। जो बदलना हो केवल उसी पंक्ति में लिख दें।</t>
         </is>
@@ -3011,14 +3117,348 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ठीक है,बदलें"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🪜 गूंगा · बहरा · लंगड़ा · अंधा · मृत — सुसंगत सीढ़ी</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>पाँचों नाम आपके दस्तावेज़ में थे पर परिभाषा नहीं। अब दृष्टि व सोया के नियम तय हैं, इसलिए इन्हें तीन गणना-योग्य संकेतों पर टिका दिया है। ये मेरी बनाई परिभाषाएँ हैं — स्क्रीन पर 'अनुमानित' लिखा रहेगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>तीन बुनियादी संकेत — इन्हीं तीन से पाँचों बनते हैं</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>संकेत</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>मतलब</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>कैसे गिना जाएगा</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>बोल</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ग्रह की बात किसी तक पहुँचती है</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>यह जिस भाव को देखता है (एकतरफ़ा दृष्टि तालिका से) उसमें कोई ग्रह बैठा हो</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>सुनना</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ग्रह तक किसी की बात पहुँचती है</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>किसी और भरे हुए भाव की दृष्टि इस ग्रह के भाव पर पड़ती हो</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>साथी</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>अकेला नहीं है</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>उसी भाव में कोई दूसरा ग्रह भी हो</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>पाँच अवस्थाएँ — कोई दो आपस में नहीं टकरातीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>अवस्था</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>शर्त (गणना-योग्य)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>फल</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>उपाय</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>सोया</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>बोल नहीं — जिस भाव को देखता है वह पूरी तरह खाली</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>कारकत्व फल नहीं दे रहा; जागृति आयु आने पर अपने-आप जागेगा</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>जागृति आयु से पहले ⇒ उस भाव की चाबी वाले ग्रह को सक्रिय करें</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>गूंगा</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>सोया + दोनों पड़ोसी भाव (उससे 2रा व 12वाँ) भी खाली</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>बोलने वाला है पर सुनने वाला कोई नहीं — कारकत्व लगभग निष्फल</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>जिस भाव को देखता है उसमें इसी ग्रह की स्थापना-वस्तु रखें — आवाज़ को जगह मिलेगी</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>बहरा</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>सुनना नहीं — कोई भरा हुआ भाव इसे नहीं देखता</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>सलाह व मदद नहीं पहुँचती; उपाय का असर बहुत धीमा</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>जो भाव इसे देखता है (पर खाली है) उसके कारक ग्रह की सेवा — कान खुलेंगे</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>लंगड़ा</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>कच्चे घर में + नीच या पीड़ित</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>फल मिलता तो है, पर बहुत देर से — चाल की समस्या है, संपर्क की नहीं</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>उसी ग्रह की स्थापना-वस्तु से बल दें</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>अंधा</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>गूंगा भी और बहरा भी — न बोल, न सुनना</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>किसी से कोई संपर्क नहीं; फल अप्रत्याशित या उल्टा</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ऊपर के दोनों उपाय एक साथ (गूंगा + बहरा)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>मृत</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>अंधा + अकेला (कोई साथी ग्रह नहीं)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>पूर्ण एकांत — कारकत्व अनुपस्थित मानें। सबसे दुर्लभ व सबसे कठोर श्रेणी</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>सर्वोच्च प्राथमिकता — स्थापना-वस्तु + कारक भाव की सेवा + उस ग्रह का दान, तीनों</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>🔎 क्यों यह सीढ़ी टिकाऊ है — तीनों संकेत उसी एकतरफ़ा दृष्टि तालिका से निकलते हैं जो आपने पुष्ट की है। इसलिए दृष्टि ठीक होते ही ये पाँचों अपने-आप चलने लगेंगे, अलग डेटा की ज़रूरत नहीं। और चूँकि शर्तें एक-दूसरे के ऊपर चढ़ती हैं (सोया ⊂ गूंगा ⊂ अंधा ⊂ मृत), कोई ग्रह दो श्रेणियों में एक साथ नहीं गिरेगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ 'सोया' आपकी दी हुई परिभाषा है — बाकी चार मेरी। जब आप असली परिभाषाएँ दें, केवल इस शीट की शर्तें बदलनी होंगी; उपाय व बाकी ढाँचा वैसा ही चलेगा।</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>